--- a/jogos_2025-07-26.xlsx
+++ b/jogos_2025-07-26.xlsx
@@ -250,15 +250,15 @@
     <t>Australia New South Wales NPL</t>
   </si>
   <si>
+    <t>South Korea K League 1</t>
+  </si>
+  <si>
     <t>South Korea K League 2</t>
   </si>
   <si>
     <t>China China League One</t>
   </si>
   <si>
-    <t>South Korea K League 1</t>
-  </si>
-  <si>
     <t>China Chinese Super League</t>
   </si>
   <si>
@@ -268,45 +268,45 @@
     <t>Norway First Division</t>
   </si>
   <si>
+    <t>Russia FNL</t>
+  </si>
+  <si>
     <t>Russia Russian Premier League</t>
   </si>
   <si>
-    <t>Russia FNL</t>
-  </si>
-  <si>
     <t>Poland Ekstraklasa</t>
   </si>
   <si>
     <t>Sweden Superettan</t>
   </si>
   <si>
+    <t>Sweden Allsvenskan</t>
+  </si>
+  <si>
+    <t>Poland 1. Liga</t>
+  </si>
+  <si>
     <t>Kazakhstan Kazakhstan Premier League</t>
   </si>
   <si>
-    <t>Sweden Allsvenskan</t>
-  </si>
-  <si>
     <t>Serbia SuperLiga</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
     <t>Belgium Pro League</t>
   </si>
   <si>
+    <t>Czech Republic First League</t>
+  </si>
+  <si>
+    <t>Czech Republic FNL</t>
+  </si>
+  <si>
     <t>Bosnia and Herzegovina Premier League of Bosnia</t>
   </si>
   <si>
-    <t>Czech Republic FNL</t>
-  </si>
-  <si>
-    <t>Czech Republic First League</t>
-  </si>
-  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
@@ -316,21 +316,21 @@
     <t>Hungary NB I</t>
   </si>
   <si>
+    <t>Slovakia Super Liga</t>
+  </si>
+  <si>
+    <t>Bulgaria First League</t>
+  </si>
+  <si>
+    <t>Switzerland Challenge League</t>
+  </si>
+  <si>
+    <t>Switzerland Super League</t>
+  </si>
+  <si>
     <t>Denmark Superliga</t>
   </si>
   <si>
-    <t>Slovakia Super Liga</t>
-  </si>
-  <si>
-    <t>Switzerland Super League</t>
-  </si>
-  <si>
-    <t>Switzerland Challenge League</t>
-  </si>
-  <si>
-    <t>Bulgaria First League</t>
-  </si>
-  <si>
     <t>Chile Primera B</t>
   </si>
   <si>
@@ -343,12 +343,12 @@
     <t>Chile Primera División</t>
   </si>
   <si>
+    <t>USA MLS Next Pro</t>
+  </si>
+  <si>
     <t>Brazil Serie C</t>
   </si>
   <si>
-    <t>USA MLS Next Pro</t>
-  </si>
-  <si>
     <t>Canada Canadian Premier League</t>
   </si>
   <si>
@@ -379,171 +379,171 @@
     <t>Marconi Stallions</t>
   </si>
   <si>
+    <t>Suwon</t>
+  </si>
+  <si>
+    <t>Asan Mugunghwa</t>
+  </si>
+  <si>
+    <t>Yanbian Longding</t>
+  </si>
+  <si>
+    <t>Cheonan City</t>
+  </si>
+  <si>
+    <t>Sangju Sangmu</t>
+  </si>
+  <si>
+    <t>Gwangju</t>
+  </si>
+  <si>
     <t>Busan I'Park</t>
   </si>
   <si>
-    <t>Cheonan City</t>
-  </si>
-  <si>
     <t>Cheongju</t>
   </si>
   <si>
-    <t>Yanbian Longding</t>
-  </si>
-  <si>
-    <t>Asan Mugunghwa</t>
-  </si>
-  <si>
-    <t>Gwangju</t>
-  </si>
-  <si>
-    <t>Suwon</t>
-  </si>
-  <si>
-    <t>Sangju Sangmu</t>
+    <t>Shaanxi Union</t>
   </si>
   <si>
     <t>Shanghai SIPG</t>
   </si>
   <si>
-    <t>Shaanxi Union</t>
+    <t>Chongqing Tongliang Long</t>
   </si>
   <si>
     <t>Hebei Kungfu</t>
   </si>
   <si>
-    <t>Chongqing Tongliang Long</t>
-  </si>
-  <si>
     <t>Chengdu Better City FC</t>
   </si>
   <si>
     <t>Haka</t>
   </si>
   <si>
+    <t>Yunnan Yukun</t>
+  </si>
+  <si>
+    <t>Ranheim</t>
+  </si>
+  <si>
+    <t>Sogndal</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
     <t>Åsane</t>
   </si>
   <si>
+    <t>Raufoss</t>
+  </si>
+  <si>
     <t>Mjøndalen</t>
   </si>
   <si>
+    <t>Chelyabinsk</t>
+  </si>
+  <si>
     <t>Aalesund</t>
   </si>
   <si>
-    <t>Start</t>
-  </si>
-  <si>
-    <t>Sogndal</t>
+    <t>Spartak Moskva</t>
   </si>
   <si>
     <t>Egersund</t>
   </si>
   <si>
-    <t>Ranheim</t>
-  </si>
-  <si>
-    <t>Yunnan Yukun</t>
-  </si>
-  <si>
-    <t>Spartak Moskva</t>
-  </si>
-  <si>
-    <t>Chelyabinsk</t>
-  </si>
-  <si>
-    <t>Raufoss</t>
-  </si>
-  <si>
     <t>Piast Gliwice</t>
   </si>
   <si>
+    <t>Oddevold</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>Wisła Kraków</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
     <t>GIF Sundsvall</t>
   </si>
   <si>
+    <t>Yelimay Semey</t>
+  </si>
+  <si>
     <t>Tobol</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>Oddevold</t>
-  </si>
-  <si>
-    <t>Yelimay Semey</t>
-  </si>
-  <si>
     <t>Javor Ivanjica</t>
   </si>
   <si>
     <t>Mariehamn</t>
   </si>
   <si>
-    <t>Wisła Kraków</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
     <t>Sandefjord</t>
   </si>
   <si>
+    <t>Kristiansund</t>
+  </si>
+  <si>
     <t>Haugesund</t>
   </si>
   <si>
-    <t>Kristiansund</t>
-  </si>
-  <si>
     <t>FCV Dender EH</t>
   </si>
   <si>
     <t>Dinamo Moskva</t>
   </si>
   <si>
+    <t>Kaisar</t>
+  </si>
+  <si>
+    <t>Sigma Olomouc</t>
+  </si>
+  <si>
+    <t>Hradec Králové</t>
+  </si>
+  <si>
     <t>Brage</t>
   </si>
   <si>
+    <t>Opava</t>
+  </si>
+  <si>
+    <t>Zlín</t>
+  </si>
+  <si>
+    <t>Zrinjski</t>
+  </si>
+  <si>
+    <t>Viktoria Plzeň</t>
+  </si>
+  <si>
+    <t>Volga Ulyanovsk</t>
+  </si>
+  <si>
+    <t>Željezničar</t>
+  </si>
+  <si>
+    <t>Sloga Doboj</t>
+  </si>
+  <si>
+    <t>Domžale</t>
+  </si>
+  <si>
+    <t>Široki Brijeg</t>
+  </si>
+  <si>
+    <t>Borac Banja Luka</t>
+  </si>
+  <si>
     <t>Sokol Saratov</t>
   </si>
   <si>
-    <t>Željezničar</t>
-  </si>
-  <si>
-    <t>Sloga Doboj</t>
-  </si>
-  <si>
-    <t>Opava</t>
-  </si>
-  <si>
-    <t>Sigma Olomouc</t>
-  </si>
-  <si>
-    <t>Zlín</t>
-  </si>
-  <si>
-    <t>Hradec Králové</t>
-  </si>
-  <si>
-    <t>Široki Brijeg</t>
-  </si>
-  <si>
-    <t>Domžale</t>
-  </si>
-  <si>
-    <t>Zrinjski</t>
-  </si>
-  <si>
-    <t>Borac Banja Luka</t>
-  </si>
-  <si>
-    <t>Volga Ulyanovsk</t>
-  </si>
-  <si>
-    <t>Kaisar</t>
-  </si>
-  <si>
-    <t>Viktoria Plzeň</t>
-  </si>
-  <si>
     <t>Puszcza Niepołomice</t>
   </si>
   <si>
@@ -562,39 +562,39 @@
     <t>Zalaegerszegi TE</t>
   </si>
   <si>
+    <t>Komárno</t>
+  </si>
+  <si>
+    <t>Beroe</t>
+  </si>
+  <si>
+    <t>Stade Lausanne-Ouchy</t>
+  </si>
+  <si>
+    <t>FK Bodo - Glimt</t>
+  </si>
+  <si>
+    <t>Grasshopper</t>
+  </si>
+  <si>
+    <t>Aarau</t>
+  </si>
+  <si>
+    <t>DAC</t>
+  </si>
+  <si>
+    <t>Radnik Surdulica</t>
+  </si>
+  <si>
     <t>København</t>
   </si>
   <si>
-    <t>Radnik Surdulica</t>
-  </si>
-  <si>
-    <t>DAC</t>
-  </si>
-  <si>
-    <t>Komárno</t>
-  </si>
-  <si>
     <t>St. Gallen</t>
   </si>
   <si>
-    <t>Aarau</t>
-  </si>
-  <si>
-    <t>Stade Lausanne-Ouchy</t>
-  </si>
-  <si>
-    <t>FK Bodo - Glimt</t>
-  </si>
-  <si>
     <t>GKS Katowice</t>
   </si>
   <si>
-    <t>Grasshopper</t>
-  </si>
-  <si>
-    <t>Beroe</t>
-  </si>
-  <si>
     <t>Zulte-Waregem</t>
   </si>
   <si>
@@ -604,37 +604,43 @@
     <t>Deportes Santa Cruz</t>
   </si>
   <si>
+    <t>FK Sochi</t>
+  </si>
+  <si>
     <t>Chrobry Głogów</t>
   </si>
   <si>
-    <t>FK Sochi</t>
-  </si>
-  <si>
     <t>Tristán Suárez</t>
   </si>
   <si>
     <t>Bohemians 1905</t>
   </si>
   <si>
+    <t>Deportivo Madryn</t>
+  </si>
+  <si>
     <t>Radnički Niš</t>
   </si>
   <si>
     <t>Red Star Belgrade</t>
   </si>
   <si>
-    <t>Deportivo Madryn</t>
+    <t>MTK</t>
   </si>
   <si>
     <t>Aluminij</t>
   </si>
   <si>
-    <t>MTK</t>
+    <t>CSKA Sofia</t>
   </si>
   <si>
     <t>Lechia Gdańsk</t>
   </si>
   <si>
-    <t>CSKA Sofia</t>
+    <t>FCSB</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
   </si>
   <si>
     <t>Young Boys</t>
@@ -646,12 +652,6 @@
     <t>Talleres Remedios</t>
   </si>
   <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>FCSB</t>
-  </si>
-  <si>
     <t>RAAL La Louvière</t>
   </si>
   <si>
@@ -661,25 +661,58 @@
     <t>La Serena</t>
   </si>
   <si>
+    <t>Central Norte</t>
+  </si>
+  <si>
+    <t>All Boys</t>
+  </si>
+  <si>
+    <t>Gimnasia Mendoza</t>
+  </si>
+  <si>
+    <t>Patronato</t>
+  </si>
+  <si>
+    <t>Nueva Chicago</t>
+  </si>
+  <si>
+    <t>Gimnasia Jujuy</t>
+  </si>
+  <si>
+    <t>New York City II</t>
+  </si>
+  <si>
+    <t>Ferro Carril Oeste</t>
+  </si>
+  <si>
     <t>Los Andes</t>
   </si>
   <si>
+    <t>San Telmo</t>
+  </si>
+  <si>
+    <t>Floresta</t>
+  </si>
+  <si>
+    <t>San Martín Tucumán</t>
+  </si>
+  <si>
+    <t>Defensores de Belgrano</t>
+  </si>
+  <si>
     <t>Club Atlético Güemes</t>
   </si>
   <si>
-    <t>Gimnasia Jujuy</t>
+    <t>Agropecuario</t>
+  </si>
+  <si>
+    <t>San Miguel</t>
   </si>
   <si>
     <t>Guarani</t>
   </si>
   <si>
-    <t>Ferro Carril Oeste</t>
-  </si>
-  <si>
-    <t>San Martín Tucumán</t>
-  </si>
-  <si>
-    <t>Defensores de Belgrano</t>
+    <t>Quilmes</t>
   </si>
   <si>
     <t>Estudiantes Río Cuarto</t>
@@ -691,99 +724,66 @@
     <t>Chacarita Juniors</t>
   </si>
   <si>
-    <t>New York City II</t>
-  </si>
-  <si>
-    <t>Floresta</t>
-  </si>
-  <si>
-    <t>Nueva Chicago</t>
-  </si>
-  <si>
-    <t>San Telmo</t>
-  </si>
-  <si>
-    <t>Gimnasia Mendoza</t>
-  </si>
-  <si>
-    <t>Agropecuario</t>
-  </si>
-  <si>
-    <t>All Boys</t>
-  </si>
-  <si>
-    <t>Central Norte</t>
-  </si>
-  <si>
-    <t>San Miguel</t>
-  </si>
-  <si>
-    <t>Patronato</t>
-  </si>
-  <si>
-    <t>Quilmes</t>
-  </si>
-  <si>
     <t>Cavalry FC</t>
   </si>
   <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
     <t>Sport Recife</t>
   </si>
   <si>
+    <t>Ferroviária</t>
+  </si>
+  <si>
     <t>Everton</t>
   </si>
   <si>
-    <t>Mirassol</t>
-  </si>
-  <si>
     <t>Fortaleza</t>
   </si>
   <si>
     <t>Botafogo</t>
   </si>
   <si>
-    <t>Ferroviária</t>
+    <t>Antofagasta</t>
+  </si>
+  <si>
+    <t>Rangers</t>
+  </si>
+  <si>
+    <t>Recoleta</t>
   </si>
   <si>
     <t>San Marcos</t>
   </si>
   <si>
-    <t>Recoleta</t>
-  </si>
-  <si>
-    <t>Antofagasta</t>
-  </si>
-  <si>
-    <t>Rangers</t>
-  </si>
-  <si>
     <t>Estudiantes Caseros</t>
   </si>
   <si>
+    <t>Retrô</t>
+  </si>
+  <si>
     <t>Londrina</t>
   </si>
   <si>
-    <t>Retrô</t>
+    <t>Univ. Concepción</t>
   </si>
   <si>
     <t>Chattanooga FC</t>
   </si>
   <si>
-    <t>Univ. Concepción</t>
-  </si>
-  <si>
     <t>Inter Miami</t>
   </si>
   <si>
+    <t>CRB</t>
+  </si>
+  <si>
     <t>Atlanta United FC</t>
   </si>
   <si>
     <t>Philadelphia Union</t>
   </si>
   <si>
-    <t>CRB</t>
-  </si>
-  <si>
     <t>DC United</t>
   </si>
   <si>
@@ -796,12 +796,12 @@
     <t>Pacific FC</t>
   </si>
   <si>
+    <t>Chicago Fire</t>
+  </si>
+  <si>
     <t>St. Louis City</t>
   </si>
   <si>
-    <t>Chicago Fire</t>
-  </si>
-  <si>
     <t>Goiás</t>
   </si>
   <si>
@@ -823,171 +823,171 @@
     <t>NWS Spirit</t>
   </si>
   <si>
+    <t>Anyang</t>
+  </si>
+  <si>
+    <t>Hwaseong</t>
+  </si>
+  <si>
+    <t>Shenyang Urban</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
+    <t>Jeju United</t>
+  </si>
+  <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Bucheon 1995</t>
   </si>
   <si>
-    <t>Gyeongnam</t>
-  </si>
-  <si>
     <t>Gimpo Citizen</t>
   </si>
   <si>
-    <t>Shenyang Urban</t>
-  </si>
-  <si>
-    <t>Hwaseong</t>
-  </si>
-  <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
-    <t>Anyang</t>
-  </si>
-  <si>
-    <t>Jeju United</t>
+    <t>Dongguan United</t>
   </si>
   <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
-    <t>Dongguan United</t>
+    <t>Shenzhen Juniors</t>
   </si>
   <si>
     <t>Shanghai Jiading</t>
   </si>
   <si>
-    <t>Shenzhen Juniors</t>
-  </si>
-  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
     <t>KTP</t>
   </si>
   <si>
+    <t>Sichuan Jiuniu</t>
+  </si>
+  <si>
+    <t>Odd</t>
+  </si>
+  <si>
+    <t>Stabæk</t>
+  </si>
+  <si>
+    <t>Lillestrøm</t>
+  </si>
+  <si>
     <t>Hødd</t>
   </si>
   <si>
+    <t>Skeid</t>
+  </si>
+  <si>
     <t>Kongsvinger</t>
   </si>
   <si>
+    <t>Rotor Volgograd</t>
+  </si>
+  <si>
     <t>Moss</t>
   </si>
   <si>
-    <t>Lillestrøm</t>
-  </si>
-  <si>
-    <t>Stabæk</t>
+    <t>Baltika</t>
   </si>
   <si>
     <t>Lyn</t>
   </si>
   <si>
-    <t>Odd</t>
-  </si>
-  <si>
-    <t>Sichuan Jiuniu</t>
-  </si>
-  <si>
-    <t>Baltika</t>
-  </si>
-  <si>
-    <t>Rotor Volgograd</t>
-  </si>
-  <si>
-    <t>Skeid</t>
-  </si>
-  <si>
     <t>Górnik Zabrze</t>
   </si>
   <si>
+    <t>Sandviken</t>
+  </si>
+  <si>
+    <t>Halmstad</t>
+  </si>
+  <si>
+    <t>ŁKS Łódź</t>
+  </si>
+  <si>
+    <t>Malmö FF</t>
+  </si>
+  <si>
     <t>Örebro</t>
   </si>
   <si>
+    <t>Zhetysu</t>
+  </si>
+  <si>
     <t>Kairat</t>
   </si>
   <si>
-    <t>Malmö FF</t>
-  </si>
-  <si>
-    <t>Sandviken</t>
-  </si>
-  <si>
-    <t>Zhetysu</t>
-  </si>
-  <si>
     <t>Partizan</t>
   </si>
   <si>
     <t>Oulu</t>
   </si>
   <si>
-    <t>ŁKS Łódź</t>
-  </si>
-  <si>
-    <t>Halmstad</t>
-  </si>
-  <si>
     <t>Sarpsborg 08</t>
   </si>
   <si>
+    <t>KFUM</t>
+  </si>
+  <si>
     <t>HamKam</t>
   </si>
   <si>
-    <t>KFUM</t>
-  </si>
-  <si>
     <t>Cercle Brugge</t>
   </si>
   <si>
     <t>Rostov</t>
   </si>
   <si>
+    <t>Kyzyl-Zhar</t>
+  </si>
+  <si>
+    <t>Dukla Praha</t>
+  </si>
+  <si>
+    <t>Karviná</t>
+  </si>
+  <si>
     <t>Umeå</t>
   </si>
   <si>
+    <t>České Budějovice</t>
+  </si>
+  <si>
+    <t>Slovácko</t>
+  </si>
+  <si>
+    <t>Sarajevo</t>
+  </si>
+  <si>
+    <t>Jablonec</t>
+  </si>
+  <si>
+    <t>KAMAZ</t>
+  </si>
+  <si>
+    <t>Radnik Bijeljina</t>
+  </si>
+  <si>
+    <t>Velež</t>
+  </si>
+  <si>
+    <t>Maribor</t>
+  </si>
+  <si>
+    <t>Posusje</t>
+  </si>
+  <si>
+    <t>Rudar Prijedor</t>
+  </si>
+  <si>
     <t>Chayka</t>
   </si>
   <si>
-    <t>Radnik Bijeljina</t>
-  </si>
-  <si>
-    <t>Velež</t>
-  </si>
-  <si>
-    <t>České Budějovice</t>
-  </si>
-  <si>
-    <t>Dukla Praha</t>
-  </si>
-  <si>
-    <t>Slovácko</t>
-  </si>
-  <si>
-    <t>Karviná</t>
-  </si>
-  <si>
-    <t>Posusje</t>
-  </si>
-  <si>
-    <t>Maribor</t>
-  </si>
-  <si>
-    <t>Sarajevo</t>
-  </si>
-  <si>
-    <t>Rudar Prijedor</t>
-  </si>
-  <si>
-    <t>KAMAZ</t>
-  </si>
-  <si>
-    <t>Kyzyl-Zhar</t>
-  </si>
-  <si>
-    <t>Jablonec</t>
-  </si>
-  <si>
     <t>Pogoń Grod. Mazowiecki</t>
   </si>
   <si>
@@ -1006,39 +1006,39 @@
     <t>Debrecen</t>
   </si>
   <si>
+    <t>Trenčín</t>
+  </si>
+  <si>
+    <t>CSKA 1948 Sofia</t>
+  </si>
+  <si>
+    <t>Wil</t>
+  </si>
+  <si>
+    <t>Vålerenga</t>
+  </si>
+  <si>
+    <t>Luzern</t>
+  </si>
+  <si>
+    <t>Bellinzona</t>
+  </si>
+  <si>
+    <t>Zemplín Michalovce</t>
+  </si>
+  <si>
+    <t>Bačka Topola</t>
+  </si>
+  <si>
     <t>Vejle</t>
   </si>
   <si>
-    <t>Bačka Topola</t>
-  </si>
-  <si>
-    <t>Zemplín Michalovce</t>
-  </si>
-  <si>
-    <t>Trenčín</t>
-  </si>
-  <si>
     <t>Basel</t>
   </si>
   <si>
-    <t>Bellinzona</t>
-  </si>
-  <si>
-    <t>Wil</t>
-  </si>
-  <si>
-    <t>Vålerenga</t>
-  </si>
-  <si>
     <t>Zagłębie Lubin</t>
   </si>
   <si>
-    <t>Luzern</t>
-  </si>
-  <si>
-    <t>CSKA 1948 Sofia</t>
-  </si>
-  <si>
     <t>KV Mechelen</t>
   </si>
   <si>
@@ -1048,12 +1048,12 @@
     <t>San Luis</t>
   </si>
   <si>
+    <t>Akron</t>
+  </si>
+  <si>
     <t>Polonia Bytom</t>
   </si>
   <si>
-    <t>Akron</t>
-  </si>
-  <si>
     <t>Slavia Praha</t>
   </si>
   <si>
@@ -1063,16 +1063,22 @@
     <t>OFK Beograd</t>
   </si>
   <si>
+    <t>Ferencváros</t>
+  </si>
+  <si>
     <t>Olimpija</t>
   </si>
   <si>
-    <t>Ferencváros</t>
+    <t>Spartak Varna</t>
   </si>
   <si>
     <t>Lech Poznań</t>
   </si>
   <si>
-    <t>Spartak Varna</t>
+    <t>SSC Farul</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
   </si>
   <si>
     <t>Servette</t>
@@ -1081,12 +1087,6 @@
     <t>Slovan Bratislava</t>
   </si>
   <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>SSC Farul</t>
-  </si>
-  <si>
     <t>Standard Liège</t>
   </si>
   <si>
@@ -1096,114 +1096,114 @@
     <t>Cobresal</t>
   </si>
   <si>
+    <t>Chaco For Ever</t>
+  </si>
+  <si>
+    <t>Club Atlético Mitre</t>
+  </si>
+  <si>
+    <t>Alvarado</t>
+  </si>
+  <si>
+    <t>Almirante Brown</t>
+  </si>
+  <si>
     <t>Gimnasia y Tiro</t>
   </si>
   <si>
+    <t>Colón</t>
+  </si>
+  <si>
+    <t>Philadelphia Union II</t>
+  </si>
+  <si>
     <t>Racing Córdoba</t>
   </si>
   <si>
-    <t>Colón</t>
+    <t>Defensores Unidos</t>
+  </si>
+  <si>
+    <t>ABC</t>
+  </si>
+  <si>
+    <t>Deportivo Maipú</t>
+  </si>
+  <si>
+    <t>Deportivo Morón</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t>Colegiales</t>
   </si>
   <si>
     <t>Náutico</t>
   </si>
   <si>
-    <t>Deportivo Maipú</t>
-  </si>
-  <si>
-    <t>Deportivo Morón</t>
+    <t>Atlanta</t>
   </si>
   <si>
     <t>Arsenal de Sarandí</t>
   </si>
   <si>
-    <t>Philadelphia Union II</t>
-  </si>
-  <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>Almirante Brown</t>
-  </si>
-  <si>
-    <t>Defensores Unidos</t>
-  </si>
-  <si>
-    <t>Club Atlético Mitre</t>
-  </si>
-  <si>
-    <t>Temperley</t>
-  </si>
-  <si>
-    <t>Chaco For Ever</t>
-  </si>
-  <si>
-    <t>Colegiales</t>
-  </si>
-  <si>
-    <t>Alvarado</t>
-  </si>
-  <si>
-    <t>Atlanta</t>
-  </si>
-  <si>
     <t>York9 FC</t>
   </si>
   <si>
+    <t>Vitória</t>
+  </si>
+  <si>
     <t>Santos</t>
   </si>
   <si>
+    <t>Operário PR</t>
+  </si>
+  <si>
     <t>Huachipato</t>
   </si>
   <si>
-    <t>Vitória</t>
-  </si>
-  <si>
     <t>Bragantino</t>
   </si>
   <si>
     <t>Corinthians</t>
   </si>
   <si>
-    <t>Operário PR</t>
+    <t>Santiago Wanderers</t>
+  </si>
+  <si>
+    <t>Copiapó</t>
+  </si>
+  <si>
+    <t>Concepción</t>
   </si>
   <si>
     <t>Magallanes</t>
   </si>
   <si>
-    <t>Concepción</t>
-  </si>
-  <si>
-    <t>Santiago Wanderers</t>
-  </si>
-  <si>
-    <t>Copiapó</t>
+    <t>Ypiranga Erechim</t>
   </si>
   <si>
     <t>CSA</t>
   </si>
   <si>
-    <t>Ypiranga Erechim</t>
+    <t>Cobreloa</t>
   </si>
   <si>
     <t>Crown Legacy</t>
   </si>
   <si>
-    <t>Cobreloa</t>
-  </si>
-  <si>
     <t>FC Cincinnati</t>
   </si>
   <si>
+    <t>Novorizontino</t>
+  </si>
+  <si>
     <t>Seattle Sounders</t>
   </si>
   <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
-    <t>Novorizontino</t>
-  </si>
-  <si>
     <t>Austin</t>
   </si>
   <si>
@@ -1216,10 +1216,10 @@
     <t>Atlético Ottawa</t>
   </si>
   <si>
+    <t>New York RB</t>
+  </si>
+  <si>
     <t>Minnesota United</t>
-  </si>
-  <si>
-    <t>New York RB</t>
   </si>
   <si>
     <t>Remo</t>
@@ -1755,76 +1755,76 @@
         <v>405</v>
       </c>
       <c r="L2">
-        <v>3.31</v>
+        <v>3.47</v>
       </c>
       <c r="M2">
+        <v>3.51</v>
+      </c>
+      <c r="N2">
+        <v>1.73</v>
+      </c>
+      <c r="O2">
+        <v>2.42</v>
+      </c>
+      <c r="P2">
+        <v>16.5</v>
+      </c>
+      <c r="Q2">
+        <v>1.56</v>
+      </c>
+      <c r="R2">
+        <v>1.29</v>
+      </c>
+      <c r="S2">
+        <v>3.3</v>
+      </c>
+      <c r="T2">
+        <v>2.3</v>
+      </c>
+      <c r="U2">
+        <v>1.55</v>
+      </c>
+      <c r="V2">
+        <v>5.25</v>
+      </c>
+      <c r="W2">
+        <v>1.12</v>
+      </c>
+      <c r="X2">
+        <v>1.01</v>
+      </c>
+      <c r="Y2">
+        <v>14</v>
+      </c>
+      <c r="Z2">
+        <v>1.18</v>
+      </c>
+      <c r="AA2">
+        <v>4.33</v>
+      </c>
+      <c r="AB2">
+        <v>1.57</v>
+      </c>
+      <c r="AC2">
+        <v>2.24</v>
+      </c>
+      <c r="AD2">
+        <v>2.38</v>
+      </c>
+      <c r="AE2">
+        <v>1.5</v>
+      </c>
+      <c r="AF2">
+        <v>1.57</v>
+      </c>
+      <c r="AG2">
+        <v>2.25</v>
+      </c>
+      <c r="AH2">
         <v>4</v>
       </c>
-      <c r="N2">
-        <v>1.82</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ2" t="s">
         <v>407</v>
@@ -1871,23 +1871,23 @@
         <v>405</v>
       </c>
       <c r="L3">
+        <v>2.15</v>
+      </c>
+      <c r="M3">
+        <v>3.6</v>
+      </c>
+      <c r="N3">
+        <v>2.7</v>
+      </c>
+      <c r="O3">
+        <v>1.73</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
         <v>2.2</v>
       </c>
-      <c r="M3">
-        <v>3.52</v>
-      </c>
-      <c r="N3">
-        <v>2.77</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
       <c r="R3">
         <v>0</v>
       </c>
@@ -1919,10 +1919,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1987,76 +1987,76 @@
         <v>405</v>
       </c>
       <c r="L4">
-        <v>9.35</v>
+        <v>10.1</v>
       </c>
       <c r="M4">
+        <v>7</v>
+      </c>
+      <c r="N4">
+        <v>1.13</v>
+      </c>
+      <c r="O4">
+        <v>4.5</v>
+      </c>
+      <c r="P4">
+        <v>27</v>
+      </c>
+      <c r="Q4">
+        <v>1.18</v>
+      </c>
+      <c r="R4">
+        <v>1.15</v>
+      </c>
+      <c r="S4">
+        <v>4.33</v>
+      </c>
+      <c r="T4">
+        <v>1.93</v>
+      </c>
+      <c r="U4">
+        <v>1.8</v>
+      </c>
+      <c r="V4">
+        <v>3.84</v>
+      </c>
+      <c r="W4">
+        <v>1.25</v>
+      </c>
+      <c r="X4">
+        <v>1.01</v>
+      </c>
+      <c r="Y4">
+        <v>17.5</v>
+      </c>
+      <c r="Z4">
+        <v>1.09</v>
+      </c>
+      <c r="AA4">
         <v>6</v>
       </c>
-      <c r="N4">
-        <v>1.21</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD4">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AE4">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AJ4" t="s">
         <v>407</v>
@@ -2103,76 +2103,76 @@
         <v>405</v>
       </c>
       <c r="L5">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="M5">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="N5">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ5" t="s">
         <v>407</v>
@@ -2219,76 +2219,76 @@
         <v>405</v>
       </c>
       <c r="L6">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="M6">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N6">
-        <v>2.69</v>
+        <v>3.2</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AB6">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AC6">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>6.72</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ6" t="s">
         <v>407</v>
@@ -2308,7 +2308,7 @@
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
         <v>115</v>
@@ -2335,76 +2335,76 @@
         <v>405</v>
       </c>
       <c r="L7">
-        <v>2.44</v>
+        <v>1.65</v>
       </c>
       <c r="M7">
-        <v>3.21</v>
+        <v>3.58</v>
       </c>
       <c r="N7">
-        <v>2.51</v>
+        <v>4.3</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB7">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC7">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ7" t="s">
         <v>407</v>
@@ -2424,7 +2424,7 @@
         <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
         <v>115</v>
@@ -2567,76 +2567,76 @@
         <v>405</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ9" t="s">
         <v>407</v>
@@ -2683,13 +2683,13 @@
         <v>405</v>
       </c>
       <c r="L10">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2731,10 +2731,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC10">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -2772,7 +2772,7 @@
         <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
         <v>115</v>
@@ -2888,7 +2888,7 @@
         <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
         <v>115</v>
@@ -2915,76 +2915,76 @@
         <v>405</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ12" t="s">
         <v>407</v>
@@ -3004,7 +3004,7 @@
         <v>41</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
         <v>115</v>
@@ -3031,76 +3031,76 @@
         <v>405</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ13" t="s">
         <v>407</v>
@@ -3120,7 +3120,7 @@
         <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
         <v>115</v>
@@ -3147,13 +3147,13 @@
         <v>405</v>
       </c>
       <c r="L14">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -3201,10 +3201,10 @@
         <v>0</v>
       </c>
       <c r="AD14">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF14">
         <v>0</v>
@@ -3236,7 +3236,7 @@
         <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
         <v>115</v>
@@ -3263,40 +3263,40 @@
         <v>405</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X15">
         <v>0</v>
@@ -3305,34 +3305,34 @@
         <v>0</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ15" t="s">
         <v>407</v>
@@ -3352,7 +3352,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
         <v>115</v>
@@ -3468,7 +3468,7 @@
         <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D17" t="s">
         <v>115</v>
@@ -3620,43 +3620,43 @@
         <v>3</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>16.75</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB18">
         <v>1.63</v>
@@ -3665,22 +3665,22 @@
         <v>2.28</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ18" t="s">
         <v>407</v>
@@ -3727,76 +3727,76 @@
         <v>405</v>
       </c>
       <c r="L19">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M19">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N19">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>14.9</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB19">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC19">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ19" t="s">
         <v>407</v>
@@ -3816,7 +3816,7 @@
         <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
         <v>115</v>
@@ -3843,76 +3843,76 @@
         <v>405</v>
       </c>
       <c r="L20">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="M20">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="N20">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB20">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AC20">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ20" t="s">
         <v>407</v>
@@ -3959,76 +3959,76 @@
         <v>405</v>
       </c>
       <c r="L21">
-        <v>5.6</v>
+        <v>2.34</v>
       </c>
       <c r="M21">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="N21">
-        <v>1.45</v>
+        <v>2.6</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD21">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AE21">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ21" t="s">
         <v>407</v>
@@ -4075,76 +4075,76 @@
         <v>405</v>
       </c>
       <c r="L22">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="M22">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N22">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AC22">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AJ22" t="s">
         <v>407</v>
@@ -4191,76 +4191,76 @@
         <v>405</v>
       </c>
       <c r="L23">
-        <v>3.15</v>
+        <v>3.38</v>
       </c>
       <c r="M23">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N23">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>17.75</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB23">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC23">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ23" t="s">
         <v>407</v>
@@ -4307,76 +4307,76 @@
         <v>405</v>
       </c>
       <c r="L24">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="M24">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="N24">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD24">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="AE24">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ24" t="s">
         <v>407</v>
@@ -4423,76 +4423,76 @@
         <v>405</v>
       </c>
       <c r="L25">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="M25">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="N25">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB25">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AC25">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI25">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ25" t="s">
         <v>407</v>
@@ -4539,76 +4539,76 @@
         <v>405</v>
       </c>
       <c r="L26">
-        <v>2.24</v>
+        <v>5.2</v>
       </c>
       <c r="M26">
-        <v>3.7</v>
+        <v>4.66</v>
       </c>
       <c r="N26">
-        <v>2.75</v>
+        <v>1.48</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AB26">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="AC26">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AD26">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AE26">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AJ26" t="s">
         <v>407</v>
@@ -4628,10 +4628,10 @@
         <v>45</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s">
         <v>142</v>
@@ -4655,76 +4655,76 @@
         <v>405</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ27" t="s">
         <v>407</v>
@@ -4744,10 +4744,10 @@
         <v>45</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s">
         <v>143</v>
@@ -4771,76 +4771,76 @@
         <v>405</v>
       </c>
       <c r="L28">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="M28">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="N28">
-        <v>6.6</v>
+        <v>3.55</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB28">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AC28">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ28" t="s">
         <v>407</v>
@@ -4887,40 +4887,40 @@
         <v>405</v>
       </c>
       <c r="L29">
-        <v>2.68</v>
+        <v>1.47</v>
       </c>
       <c r="M29">
-        <v>3.26</v>
+        <v>4.2</v>
       </c>
       <c r="N29">
-        <v>2.68</v>
+        <v>6.6</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>12.75</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
         <v>0</v>
@@ -4929,34 +4929,34 @@
         <v>0</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AB29">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="AC29">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ29" t="s">
         <v>407</v>
@@ -5003,76 +5003,76 @@
         <v>405</v>
       </c>
       <c r="L30">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="M30">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N30">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>16.25</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB30">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AC30">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ30" t="s">
         <v>407</v>
@@ -5119,76 +5119,76 @@
         <v>405</v>
       </c>
       <c r="L31">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="M31">
-        <v>3.04</v>
+        <v>3.35</v>
       </c>
       <c r="N31">
-        <v>2.53</v>
+        <v>3.05</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB31">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AC31">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AJ31" t="s">
         <v>407</v>
@@ -5235,76 +5235,76 @@
         <v>405</v>
       </c>
       <c r="L32">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="M32">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N32">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB32">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AC32">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI32">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ32" t="s">
         <v>407</v>
@@ -5351,76 +5351,76 @@
         <v>405</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH33">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AI33">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AJ33" t="s">
         <v>407</v>
@@ -5443,7 +5443,7 @@
         <v>89</v>
       </c>
       <c r="D34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E34" t="s">
         <v>149</v>
@@ -5467,76 +5467,76 @@
         <v>405</v>
       </c>
       <c r="L34">
+        <v>1.47</v>
+      </c>
+      <c r="M34">
+        <v>4.3</v>
+      </c>
+      <c r="N34">
+        <v>5.8</v>
+      </c>
+      <c r="O34">
+        <v>1.42</v>
+      </c>
+      <c r="P34">
+        <v>13</v>
+      </c>
+      <c r="Q34">
+        <v>3.1</v>
+      </c>
+      <c r="R34">
+        <v>1.31</v>
+      </c>
+      <c r="S34">
+        <v>3.3</v>
+      </c>
+      <c r="T34">
+        <v>2.32</v>
+      </c>
+      <c r="U34">
+        <v>1.55</v>
+      </c>
+      <c r="V34">
+        <v>5</v>
+      </c>
+      <c r="W34">
+        <v>1.12</v>
+      </c>
+      <c r="X34">
+        <v>1.02</v>
+      </c>
+      <c r="Y34">
+        <v>12</v>
+      </c>
+      <c r="Z34">
+        <v>1.18</v>
+      </c>
+      <c r="AA34">
+        <v>4.3</v>
+      </c>
+      <c r="AB34">
+        <v>1.61</v>
+      </c>
+      <c r="AC34">
+        <v>2.25</v>
+      </c>
+      <c r="AD34">
+        <v>2.35</v>
+      </c>
+      <c r="AE34">
+        <v>1.5</v>
+      </c>
+      <c r="AF34">
+        <v>1.68</v>
+      </c>
+      <c r="AG34">
+        <v>2.01</v>
+      </c>
+      <c r="AH34">
         <v>4.1</v>
       </c>
-      <c r="M34">
-        <v>3.76</v>
-      </c>
-      <c r="N34">
-        <v>1.64</v>
-      </c>
-      <c r="O34">
-        <v>0</v>
-      </c>
-      <c r="P34">
-        <v>0</v>
-      </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>0</v>
-      </c>
-      <c r="AB34">
-        <v>1.76</v>
-      </c>
-      <c r="AC34">
-        <v>1.94</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AE34">
-        <v>0</v>
-      </c>
-      <c r="AF34">
-        <v>0</v>
-      </c>
-      <c r="AG34">
-        <v>0</v>
-      </c>
-      <c r="AH34">
-        <v>0</v>
-      </c>
       <c r="AI34">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ34" t="s">
         <v>407</v>
@@ -5556,7 +5556,7 @@
         <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
         <v>115</v>
@@ -5583,76 +5583,76 @@
         <v>405</v>
       </c>
       <c r="L35">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="M35">
-        <v>3.3</v>
+        <v>3.76</v>
       </c>
       <c r="N35">
+        <v>1.64</v>
+      </c>
+      <c r="O35">
+        <v>2.4</v>
+      </c>
+      <c r="P35">
+        <v>11.5</v>
+      </c>
+      <c r="Q35">
+        <v>1.57</v>
+      </c>
+      <c r="R35">
+        <v>1.3</v>
+      </c>
+      <c r="S35">
+        <v>3.4</v>
+      </c>
+      <c r="T35">
+        <v>2.38</v>
+      </c>
+      <c r="U35">
+        <v>1.53</v>
+      </c>
+      <c r="V35">
+        <v>6</v>
+      </c>
+      <c r="W35">
+        <v>1.13</v>
+      </c>
+      <c r="X35">
+        <v>1.04</v>
+      </c>
+      <c r="Y35">
+        <v>11</v>
+      </c>
+      <c r="Z35">
+        <v>1.22</v>
+      </c>
+      <c r="AA35">
+        <v>4.33</v>
+      </c>
+      <c r="AB35">
+        <v>1.76</v>
+      </c>
+      <c r="AC35">
+        <v>1.94</v>
+      </c>
+      <c r="AD35">
         <v>2.7</v>
       </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>0</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
-      <c r="AA35">
-        <v>0</v>
-      </c>
-      <c r="AB35">
-        <v>1.89</v>
-      </c>
-      <c r="AC35">
-        <v>1.88</v>
-      </c>
-      <c r="AD35">
-        <v>0</v>
-      </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ35" t="s">
         <v>407</v>
@@ -5672,7 +5672,7 @@
         <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D36" t="s">
         <v>115</v>
@@ -5699,76 +5699,76 @@
         <v>405</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH36">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI36">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ36" t="s">
         <v>407</v>
@@ -5791,7 +5791,7 @@
         <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E37" t="s">
         <v>152</v>
@@ -5904,7 +5904,7 @@
         <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D38" t="s">
         <v>115</v>
@@ -5931,13 +5931,13 @@
         <v>405</v>
       </c>
       <c r="L38">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="M38">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N38">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -5979,10 +5979,10 @@
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD38">
         <v>0</v>
@@ -6047,13 +6047,13 @@
         <v>405</v>
       </c>
       <c r="L39">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M39">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N39">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -6136,7 +6136,7 @@
         <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="D40" t="s">
         <v>115</v>
@@ -6163,76 +6163,76 @@
         <v>405</v>
       </c>
       <c r="L40">
-        <v>1.49</v>
+        <v>2.8</v>
       </c>
       <c r="M40">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="N40">
-        <v>5.1</v>
+        <v>2.38</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB40">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC40">
         <v>1.95</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AH40">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ40" t="s">
         <v>407</v>
@@ -6288,43 +6288,43 @@
         <v>2.57</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB41">
         <v>1.5</v>
@@ -6339,16 +6339,16 @@
         <v>1.53</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH41">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AJ41" t="s">
         <v>407</v>
@@ -6395,76 +6395,76 @@
         <v>405</v>
       </c>
       <c r="L42">
-        <v>2.89</v>
+        <v>3.01</v>
       </c>
       <c r="M42">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="N42">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AB42">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AC42">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI42">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AJ42" t="s">
         <v>407</v>
@@ -6511,76 +6511,76 @@
         <v>405</v>
       </c>
       <c r="L43">
-        <v>3.01</v>
+        <v>2.89</v>
       </c>
       <c r="M43">
-        <v>3.11</v>
+        <v>3.23</v>
       </c>
       <c r="N43">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB43">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AC43">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH43">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI43">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AJ43" t="s">
         <v>407</v>
@@ -6636,43 +6636,43 @@
         <v>2.24</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB44">
         <v>1.85</v>
@@ -6681,22 +6681,22 @@
         <v>1.85</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH44">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AI44">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ44" t="s">
         <v>407</v>
@@ -6716,7 +6716,7 @@
         <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D45" t="s">
         <v>116</v>
@@ -6752,31 +6752,31 @@
         <v>4.5</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X45">
         <v>0</v>
@@ -6785,16 +6785,16 @@
         <v>0</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD45">
         <v>2.22</v>
@@ -6803,16 +6803,16 @@
         <v>1.66</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH45">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI45">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ45" t="s">
         <v>407</v>
@@ -6832,7 +6832,7 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
         <v>115</v>
@@ -6859,13 +6859,13 @@
         <v>405</v>
       </c>
       <c r="L46">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M46">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N46">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -6907,10 +6907,10 @@
         <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD46">
         <v>0</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D47" t="s">
         <v>116</v>
@@ -6975,76 +6975,76 @@
         <v>405</v>
       </c>
       <c r="L47">
-        <v>2.05</v>
+        <v>1.56</v>
       </c>
       <c r="M47">
-        <v>3.13</v>
+        <v>4.15</v>
       </c>
       <c r="N47">
-        <v>3.95</v>
+        <v>5.45</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>13.75</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH47">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AI47">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ47" t="s">
         <v>407</v>
@@ -7091,76 +7091,76 @@
         <v>405</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>14.25</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH48">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AI48">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ48" t="s">
         <v>407</v>
@@ -7180,10 +7180,10 @@
         <v>50</v>
       </c>
       <c r="C49" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D49" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E49" t="s">
         <v>164</v>
@@ -7207,76 +7207,76 @@
         <v>405</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH49">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI49">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ49" t="s">
         <v>407</v>
@@ -7412,7 +7412,7 @@
         <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D51" t="s">
         <v>116</v>
@@ -7439,76 +7439,76 @@
         <v>405</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M51">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH51">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AI51">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ51" t="s">
         <v>407</v>
@@ -7644,7 +7644,7 @@
         <v>50</v>
       </c>
       <c r="C53" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D53" t="s">
         <v>116</v>
@@ -7671,76 +7671,76 @@
         <v>405</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M53">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH53">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AI53">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AJ53" t="s">
         <v>407</v>
@@ -7760,7 +7760,7 @@
         <v>50</v>
       </c>
       <c r="C54" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D54" t="s">
         <v>116</v>
@@ -7787,76 +7787,76 @@
         <v>405</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M54">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AH54">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AI54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AJ54" t="s">
         <v>407</v>
@@ -7876,7 +7876,7 @@
         <v>50</v>
       </c>
       <c r="C55" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D55" t="s">
         <v>116</v>
@@ -7903,13 +7903,13 @@
         <v>405</v>
       </c>
       <c r="L55">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="M55">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="N55">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>50</v>
       </c>
       <c r="C56" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D56" t="s">
         <v>116</v>
@@ -8108,7 +8108,7 @@
         <v>50</v>
       </c>
       <c r="C57" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D57" t="s">
         <v>116</v>
@@ -8135,13 +8135,13 @@
         <v>405</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -8224,7 +8224,7 @@
         <v>50</v>
       </c>
       <c r="C58" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D58" t="s">
         <v>116</v>
@@ -8251,13 +8251,13 @@
         <v>405</v>
       </c>
       <c r="L58">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="M58">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N58">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="O58">
         <v>0</v>
@@ -8340,10 +8340,10 @@
         <v>50</v>
       </c>
       <c r="C59" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="D59" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E59" t="s">
         <v>174</v>
@@ -8456,7 +8456,7 @@
         <v>50</v>
       </c>
       <c r="C60" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D60" t="s">
         <v>116</v>
@@ -8483,76 +8483,76 @@
         <v>405</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH60">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AI60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ60" t="s">
         <v>407</v>
@@ -8572,7 +8572,7 @@
         <v>51</v>
       </c>
       <c r="C61" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D61" t="s">
         <v>116</v>
@@ -8617,58 +8617,58 @@
         <v>0</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH61">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI61">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ61" t="s">
         <v>407</v>
@@ -8724,31 +8724,31 @@
         <v>2.72</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P62">
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X62">
         <v>0</v>
@@ -8775,10 +8775,10 @@
         <v>0</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH62">
         <v>0</v>
@@ -8840,43 +8840,43 @@
         <v>4.1</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB63">
         <v>1.86</v>
@@ -8885,22 +8885,22 @@
         <v>1.86</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH63">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI63">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ63" t="s">
         <v>407</v>
@@ -8920,7 +8920,7 @@
         <v>51</v>
       </c>
       <c r="C64" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D64" t="s">
         <v>115</v>
@@ -8956,43 +8956,43 @@
         <v>2.62</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB64">
         <v>1.48</v>
@@ -9007,16 +9007,16 @@
         <v>1.6</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH64">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI64">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ64" t="s">
         <v>407</v>
@@ -9072,43 +9072,43 @@
         <v>4.3</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB65">
         <v>1.8</v>
@@ -9123,16 +9123,16 @@
         <v>1.43</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH65">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI65">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ65" t="s">
         <v>407</v>
@@ -9295,13 +9295,13 @@
         <v>405</v>
       </c>
       <c r="L67">
-        <v>1.23</v>
+        <v>2.46</v>
       </c>
       <c r="M67">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N67">
-        <v>8.699999999999999</v>
+        <v>2.46</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -9343,16 +9343,16 @@
         <v>0</v>
       </c>
       <c r="AB67">
-        <v>1.53</v>
+        <v>1.89</v>
       </c>
       <c r="AC67">
-        <v>2.35</v>
+        <v>1.81</v>
       </c>
       <c r="AD67">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE67">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF67">
         <v>0</v>
@@ -9384,7 +9384,7 @@
         <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="D68" t="s">
         <v>116</v>
@@ -9411,13 +9411,13 @@
         <v>405</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -9459,10 +9459,10 @@
         <v>0</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AD68">
         <v>0</v>
@@ -9500,7 +9500,7 @@
         <v>53</v>
       </c>
       <c r="C69" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D69" t="s">
         <v>116</v>
@@ -9527,13 +9527,13 @@
         <v>405</v>
       </c>
       <c r="L69">
-        <v>1.45</v>
+        <v>1.78</v>
       </c>
       <c r="M69">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="N69">
-        <v>5.88</v>
+        <v>3.58</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -9578,7 +9578,7 @@
         <v>1.6</v>
       </c>
       <c r="AC69">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD69">
         <v>0</v>
@@ -9616,10 +9616,10 @@
         <v>53</v>
       </c>
       <c r="C70" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D70" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E70" t="s">
         <v>185</v>
@@ -9643,76 +9643,76 @@
         <v>405</v>
       </c>
       <c r="L70">
-        <v>2.46</v>
+        <v>1.23</v>
       </c>
       <c r="M70">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="N70">
-        <v>2.46</v>
+        <v>7.8</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB70">
-        <v>1.89</v>
+        <v>1.28</v>
       </c>
       <c r="AC70">
-        <v>1.81</v>
+        <v>3.3</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH70">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AI70">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AJ70" t="s">
         <v>407</v>
@@ -9732,7 +9732,7 @@
         <v>53</v>
       </c>
       <c r="C71" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D71" t="s">
         <v>116</v>
@@ -9759,22 +9759,22 @@
         <v>405</v>
       </c>
       <c r="L71">
-        <v>3.23</v>
+        <v>2.21</v>
       </c>
       <c r="M71">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="N71">
-        <v>1.93</v>
+        <v>2.74</v>
       </c>
       <c r="O71">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="P71">
         <v>0</v>
       </c>
       <c r="Q71">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -9807,10 +9807,10 @@
         <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC71">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD71">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         <v>53</v>
       </c>
       <c r="C72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D72" t="s">
         <v>116</v>
@@ -9964,7 +9964,7 @@
         <v>53</v>
       </c>
       <c r="C73" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D73" t="s">
         <v>116</v>
@@ -9991,13 +9991,13 @@
         <v>405</v>
       </c>
       <c r="L73">
-        <v>1.78</v>
+        <v>1.45</v>
       </c>
       <c r="M73">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="N73">
-        <v>3.58</v>
+        <v>5.88</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -10042,7 +10042,7 @@
         <v>1.6</v>
       </c>
       <c r="AC73">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD73">
         <v>0</v>
@@ -10080,10 +10080,10 @@
         <v>53</v>
       </c>
       <c r="C74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D74" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E74" t="s">
         <v>189</v>
@@ -10107,13 +10107,13 @@
         <v>405</v>
       </c>
       <c r="L74">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M74">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="N74">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -10155,16 +10155,16 @@
         <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AC74">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD74">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE74">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF74">
         <v>0</v>
@@ -10196,7 +10196,7 @@
         <v>53</v>
       </c>
       <c r="C75" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D75" t="s">
         <v>116</v>
@@ -10223,13 +10223,13 @@
         <v>405</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -10271,16 +10271,16 @@
         <v>0</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF75">
         <v>0</v>
@@ -10312,7 +10312,7 @@
         <v>53</v>
       </c>
       <c r="C76" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D76" t="s">
         <v>116</v>
@@ -10339,58 +10339,58 @@
         <v>405</v>
       </c>
       <c r="L76">
-        <v>2.21</v>
+        <v>3.23</v>
       </c>
       <c r="M76">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="N76">
-        <v>2.74</v>
+        <v>1.93</v>
       </c>
       <c r="O76">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="P76">
         <v>0</v>
       </c>
       <c r="Q76">
+        <v>1.62</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+      <c r="AA76">
+        <v>0</v>
+      </c>
+      <c r="AB76">
+        <v>1.65</v>
+      </c>
+      <c r="AC76">
         <v>2.05</v>
-      </c>
-      <c r="R76">
-        <v>0</v>
-      </c>
-      <c r="S76">
-        <v>0</v>
-      </c>
-      <c r="T76">
-        <v>0</v>
-      </c>
-      <c r="U76">
-        <v>0</v>
-      </c>
-      <c r="V76">
-        <v>0</v>
-      </c>
-      <c r="W76">
-        <v>0</v>
-      </c>
-      <c r="X76">
-        <v>0</v>
-      </c>
-      <c r="Y76">
-        <v>0</v>
-      </c>
-      <c r="Z76">
-        <v>0</v>
-      </c>
-      <c r="AA76">
-        <v>0</v>
-      </c>
-      <c r="AB76">
-        <v>1.67</v>
-      </c>
-      <c r="AC76">
-        <v>2</v>
       </c>
       <c r="AD76">
         <v>0</v>
@@ -10428,7 +10428,7 @@
         <v>53</v>
       </c>
       <c r="C77" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D77" t="s">
         <v>116</v>
@@ -10455,13 +10455,13 @@
         <v>405</v>
       </c>
       <c r="L77">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="M77">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N77">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -10503,10 +10503,10 @@
         <v>0</v>
       </c>
       <c r="AB77">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AC77">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AD77">
         <v>0</v>
@@ -10696,43 +10696,43 @@
         <v>2.48</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB79">
         <v>2.1</v>
@@ -10741,22 +10741,22 @@
         <v>1.67</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH79">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI79">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ79" t="s">
         <v>407</v>
@@ -10812,43 +10812,43 @@
         <v>2.56</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB80">
         <v>2.25</v>
@@ -10857,22 +10857,22 @@
         <v>1.57</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH80">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AI80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ80" t="s">
         <v>407</v>
@@ -10892,7 +10892,7 @@
         <v>56</v>
       </c>
       <c r="C81" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D81" t="s">
         <v>116</v>
@@ -10919,13 +10919,13 @@
         <v>405</v>
       </c>
       <c r="L81">
-        <v>2.75</v>
+        <v>2.23</v>
       </c>
       <c r="M81">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="N81">
-        <v>2.32</v>
+        <v>2.88</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -10967,10 +10967,10 @@
         <v>0</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD81">
         <v>0</v>
@@ -11008,7 +11008,7 @@
         <v>56</v>
       </c>
       <c r="C82" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D82" t="s">
         <v>116</v>
@@ -11035,13 +11035,13 @@
         <v>405</v>
       </c>
       <c r="L82">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="M82">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="N82">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -11083,10 +11083,10 @@
         <v>0</v>
       </c>
       <c r="AB82">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC82">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD82">
         <v>0</v>
@@ -11133,7 +11133,7 @@
         <v>198</v>
       </c>
       <c r="F83" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -11240,7 +11240,7 @@
         <v>58</v>
       </c>
       <c r="C84" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D84" t="s">
         <v>116</v>
@@ -11356,16 +11356,16 @@
         <v>58</v>
       </c>
       <c r="C85" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="D85" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E85" t="s">
         <v>200</v>
       </c>
       <c r="F85" t="s">
-        <v>347</v>
+        <v>218</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -11383,13 +11383,13 @@
         <v>405</v>
       </c>
       <c r="L85">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M85">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -11472,7 +11472,7 @@
         <v>58</v>
       </c>
       <c r="C86" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D86" t="s">
         <v>116</v>
@@ -11481,7 +11481,7 @@
         <v>201</v>
       </c>
       <c r="F86" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -11588,16 +11588,16 @@
         <v>58</v>
       </c>
       <c r="C87" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D87" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E87" t="s">
         <v>202</v>
       </c>
       <c r="F87" t="s">
-        <v>234</v>
+        <v>348</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -11615,13 +11615,13 @@
         <v>405</v>
       </c>
       <c r="L87">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M87">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="N87">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -11704,7 +11704,7 @@
         <v>59</v>
       </c>
       <c r="C88" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D88" t="s">
         <v>116</v>
@@ -11731,13 +11731,13 @@
         <v>405</v>
       </c>
       <c r="L88">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="M88">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="N88">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -11779,16 +11779,16 @@
         <v>0</v>
       </c>
       <c r="AB88">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC88">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF88">
         <v>0</v>
@@ -11820,7 +11820,7 @@
         <v>59</v>
       </c>
       <c r="C89" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D89" t="s">
         <v>116</v>
@@ -11847,13 +11847,13 @@
         <v>405</v>
       </c>
       <c r="L89">
+        <v>7.8</v>
+      </c>
+      <c r="M89">
         <v>4.7</v>
       </c>
-      <c r="M89">
-        <v>4.1</v>
-      </c>
       <c r="N89">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -11895,16 +11895,16 @@
         <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AC89">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="AD89">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AF89">
         <v>0</v>
@@ -11936,7 +11936,7 @@
         <v>59</v>
       </c>
       <c r="C90" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D90" t="s">
         <v>116</v>
@@ -11963,13 +11963,13 @@
         <v>405</v>
       </c>
       <c r="L90">
-        <v>3.91</v>
+        <v>1.17</v>
       </c>
       <c r="M90">
-        <v>3.36</v>
+        <v>6</v>
       </c>
       <c r="N90">
-        <v>1.77</v>
+        <v>10</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -12011,16 +12011,16 @@
         <v>0</v>
       </c>
       <c r="AB90">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AC90">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF90">
         <v>0</v>
@@ -12052,7 +12052,7 @@
         <v>59</v>
       </c>
       <c r="C91" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D91" t="s">
         <v>116</v>
@@ -12079,13 +12079,13 @@
         <v>405</v>
       </c>
       <c r="L91">
-        <v>1.17</v>
+        <v>3.91</v>
       </c>
       <c r="M91">
-        <v>6</v>
+        <v>3.36</v>
       </c>
       <c r="N91">
-        <v>10</v>
+        <v>1.77</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -12127,10 +12127,10 @@
         <v>0</v>
       </c>
       <c r="AB91">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC91">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD91">
         <v>0</v>
@@ -12168,7 +12168,7 @@
         <v>60</v>
       </c>
       <c r="C92" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D92" t="s">
         <v>116</v>
@@ -12195,22 +12195,22 @@
         <v>405</v>
       </c>
       <c r="L92">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="M92">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="N92">
-        <v>3.21</v>
+        <v>4.4</v>
       </c>
       <c r="O92">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P92">
         <v>0</v>
       </c>
       <c r="Q92">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -12243,10 +12243,10 @@
         <v>0</v>
       </c>
       <c r="AB92">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AC92">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AD92">
         <v>0</v>
@@ -12255,10 +12255,10 @@
         <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG92">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH92">
         <v>0</v>
@@ -12284,10 +12284,10 @@
         <v>60</v>
       </c>
       <c r="C93" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D93" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E93" t="s">
         <v>208</v>
@@ -12311,13 +12311,13 @@
         <v>405</v>
       </c>
       <c r="L93">
-        <v>6</v>
+        <v>2.87</v>
       </c>
       <c r="M93">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="N93">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -12359,10 +12359,10 @@
         <v>0</v>
       </c>
       <c r="AB93">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AC93">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD93">
         <v>0</v>
@@ -12400,16 +12400,16 @@
         <v>60</v>
       </c>
       <c r="C94" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D94" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E94" t="s">
         <v>209</v>
       </c>
       <c r="F94" t="s">
-        <v>221</v>
+        <v>355</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -12424,25 +12424,25 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="L94">
-        <v>2.81</v>
+        <v>1.96</v>
       </c>
       <c r="M94">
-        <v>2.78</v>
+        <v>3.37</v>
       </c>
       <c r="N94">
-        <v>2.47</v>
+        <v>3.21</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="P94">
         <v>0</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -12469,28 +12469,28 @@
         <v>0</v>
       </c>
       <c r="Z94">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA94">
+        <v>0</v>
+      </c>
+      <c r="AB94">
+        <v>1.7</v>
+      </c>
+      <c r="AC94">
+        <v>1.95</v>
+      </c>
+      <c r="AD94">
+        <v>0</v>
+      </c>
+      <c r="AE94">
+        <v>0</v>
+      </c>
+      <c r="AF94">
+        <v>1.62</v>
+      </c>
+      <c r="AG94">
         <v>2.2</v>
-      </c>
-      <c r="AB94">
-        <v>0</v>
-      </c>
-      <c r="AC94">
-        <v>0</v>
-      </c>
-      <c r="AD94">
-        <v>0</v>
-      </c>
-      <c r="AE94">
-        <v>0</v>
-      </c>
-      <c r="AF94">
-        <v>0</v>
-      </c>
-      <c r="AG94">
-        <v>0</v>
       </c>
       <c r="AH94">
         <v>0</v>
@@ -12516,16 +12516,16 @@
         <v>60</v>
       </c>
       <c r="C95" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D95" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E95" t="s">
         <v>210</v>
       </c>
       <c r="F95" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -12543,13 +12543,13 @@
         <v>405</v>
       </c>
       <c r="L95">
-        <v>2.87</v>
+        <v>6</v>
       </c>
       <c r="M95">
-        <v>3.5</v>
+        <v>3.83</v>
       </c>
       <c r="N95">
-        <v>2.06</v>
+        <v>1.44</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -12591,10 +12591,10 @@
         <v>0</v>
       </c>
       <c r="AB95">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AC95">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD95">
         <v>0</v>
@@ -12632,16 +12632,16 @@
         <v>60</v>
       </c>
       <c r="C96" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D96" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E96" t="s">
         <v>211</v>
       </c>
       <c r="F96" t="s">
-        <v>356</v>
+        <v>227</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -12656,16 +12656,16 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L96">
-        <v>1.67</v>
+        <v>2.81</v>
       </c>
       <c r="M96">
-        <v>3.4</v>
+        <v>2.78</v>
       </c>
       <c r="N96">
-        <v>4.4</v>
+        <v>2.47</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -12701,16 +12701,16 @@
         <v>0</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB96">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AC96">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AD96">
         <v>0</v>
@@ -13102,7 +13102,7 @@
         <v>115</v>
       </c>
       <c r="E100" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="F100" t="s">
         <v>360</v>
@@ -13218,10 +13218,10 @@
         <v>115</v>
       </c>
       <c r="E101" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F101" t="s">
-        <v>361</v>
+        <v>234</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -13239,13 +13239,13 @@
         <v>405</v>
       </c>
       <c r="L101">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M101">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -13334,10 +13334,10 @@
         <v>115</v>
       </c>
       <c r="E102" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F102" t="s">
-        <v>202</v>
+        <v>361</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -13450,7 +13450,7 @@
         <v>115</v>
       </c>
       <c r="E103" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F103" t="s">
         <v>362</v>
@@ -13560,13 +13560,13 @@
         <v>63</v>
       </c>
       <c r="C104" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D104" t="s">
         <v>115</v>
       </c>
       <c r="E104" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F104" t="s">
         <v>363</v>
@@ -13682,10 +13682,10 @@
         <v>115</v>
       </c>
       <c r="E105" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="F105" t="s">
-        <v>231</v>
+        <v>364</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -13801,7 +13801,7 @@
         <v>220</v>
       </c>
       <c r="F106" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G106">
         <v>0</v>
@@ -13908,7 +13908,7 @@
         <v>63</v>
       </c>
       <c r="C107" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D107" t="s">
         <v>115</v>
@@ -13917,7 +13917,7 @@
         <v>221</v>
       </c>
       <c r="F107" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G107">
         <v>0</v>
@@ -14033,7 +14033,7 @@
         <v>222</v>
       </c>
       <c r="F108" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -14149,7 +14149,7 @@
         <v>223</v>
       </c>
       <c r="F109" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -14265,7 +14265,7 @@
         <v>224</v>
       </c>
       <c r="F110" t="s">
-        <v>247</v>
+        <v>368</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -14381,7 +14381,7 @@
         <v>225</v>
       </c>
       <c r="F111" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -14399,13 +14399,13 @@
         <v>405</v>
       </c>
       <c r="L111">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M111">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -14488,7 +14488,7 @@
         <v>63</v>
       </c>
       <c r="C112" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D112" t="s">
         <v>115</v>
@@ -14497,7 +14497,7 @@
         <v>226</v>
       </c>
       <c r="F112" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -14613,7 +14613,7 @@
         <v>227</v>
       </c>
       <c r="F113" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -14729,7 +14729,7 @@
         <v>228</v>
       </c>
       <c r="F114" t="s">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -14845,7 +14845,7 @@
         <v>229</v>
       </c>
       <c r="F115" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -14961,7 +14961,7 @@
         <v>230</v>
       </c>
       <c r="F116" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -15068,7 +15068,7 @@
         <v>63</v>
       </c>
       <c r="C117" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D117" t="s">
         <v>115</v>
@@ -15077,7 +15077,7 @@
         <v>231</v>
       </c>
       <c r="F117" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="G117">
         <v>0</v>
@@ -15095,13 +15095,13 @@
         <v>405</v>
       </c>
       <c r="L117">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="M117">
-        <v>2.85</v>
+        <v>3.04</v>
       </c>
       <c r="N117">
-        <v>4.6</v>
+        <v>3.74</v>
       </c>
       <c r="O117">
         <v>0</v>
@@ -15193,7 +15193,7 @@
         <v>232</v>
       </c>
       <c r="F118" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>233</v>
       </c>
       <c r="F119" t="s">
-        <v>374</v>
+        <v>211</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -15425,7 +15425,7 @@
         <v>234</v>
       </c>
       <c r="F120" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -15541,7 +15541,7 @@
         <v>235</v>
       </c>
       <c r="F121" t="s">
-        <v>376</v>
+        <v>247</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -15791,13 +15791,13 @@
         <v>405</v>
       </c>
       <c r="L123">
-        <v>2.49</v>
+        <v>1.83</v>
       </c>
       <c r="M123">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="N123">
-        <v>2.63</v>
+        <v>3.85</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -15833,13 +15833,13 @@
         <v>0</v>
       </c>
       <c r="Z123">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA123">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB123">
-        <v>2.53</v>
+        <v>2.37</v>
       </c>
       <c r="AC123">
         <v>1.53</v>
@@ -15880,7 +15880,7 @@
         <v>65</v>
       </c>
       <c r="C124" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D124" t="s">
         <v>115</v>
@@ -15907,13 +15907,13 @@
         <v>405</v>
       </c>
       <c r="L124">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M124">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -15949,16 +15949,16 @@
         <v>0</v>
       </c>
       <c r="Z124">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA124">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB124">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AC124">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD124">
         <v>0</v>
@@ -15996,7 +15996,7 @@
         <v>65</v>
       </c>
       <c r="C125" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D125" t="s">
         <v>115</v>
@@ -16023,13 +16023,13 @@
         <v>405</v>
       </c>
       <c r="L125">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="M125">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N125">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="O125">
         <v>0</v>
@@ -16065,16 +16065,16 @@
         <v>0</v>
       </c>
       <c r="Z125">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA125">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB125">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC125">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD125">
         <v>0</v>
@@ -16112,7 +16112,7 @@
         <v>65</v>
       </c>
       <c r="C126" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D126" t="s">
         <v>115</v>
@@ -16139,13 +16139,13 @@
         <v>405</v>
       </c>
       <c r="L126">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M126">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="N126">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -16187,10 +16187,10 @@
         <v>0</v>
       </c>
       <c r="AB126">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC126">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD126">
         <v>0</v>
@@ -16255,13 +16255,13 @@
         <v>405</v>
       </c>
       <c r="L127">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="M127">
-        <v>3.29</v>
+        <v>3.08</v>
       </c>
       <c r="N127">
-        <v>4.2</v>
+        <v>3.21</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -16297,16 +16297,16 @@
         <v>0</v>
       </c>
       <c r="Z127">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA127">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB127">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC127">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AD127">
         <v>0</v>
@@ -16344,7 +16344,7 @@
         <v>65</v>
       </c>
       <c r="C128" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D128" t="s">
         <v>115</v>
@@ -16371,13 +16371,13 @@
         <v>405</v>
       </c>
       <c r="L128">
-        <v>2.23</v>
+        <v>1.73</v>
       </c>
       <c r="M128">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="N128">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -16413,16 +16413,16 @@
         <v>0</v>
       </c>
       <c r="Z128">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AA128">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AB128">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC128">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD128">
         <v>0</v>
@@ -16933,7 +16933,7 @@
         <v>247</v>
       </c>
       <c r="F133" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -16951,13 +16951,13 @@
         <v>405</v>
       </c>
       <c r="L133">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="M133">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="N133">
-        <v>5.21</v>
+        <v>5</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -17040,7 +17040,7 @@
         <v>68</v>
       </c>
       <c r="C134" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D134" t="s">
         <v>115</v>
@@ -17067,13 +17067,13 @@
         <v>405</v>
       </c>
       <c r="L134">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M134">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N134">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O134">
         <v>0</v>
@@ -17156,7 +17156,7 @@
         <v>68</v>
       </c>
       <c r="C135" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D135" t="s">
         <v>115</v>
@@ -17183,13 +17183,13 @@
         <v>405</v>
       </c>
       <c r="L135">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M135">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N135">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -17272,7 +17272,7 @@
         <v>69</v>
       </c>
       <c r="C136" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D136" t="s">
         <v>115</v>
@@ -17299,13 +17299,13 @@
         <v>405</v>
       </c>
       <c r="L136">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M136">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O136">
         <v>0</v>
@@ -17347,10 +17347,10 @@
         <v>0</v>
       </c>
       <c r="AB136">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC136">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD136">
         <v>0</v>
@@ -17388,7 +17388,7 @@
         <v>69</v>
       </c>
       <c r="C137" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D137" t="s">
         <v>115</v>
@@ -17415,13 +17415,13 @@
         <v>405</v>
       </c>
       <c r="L137">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M137">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N137">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="O137">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="AB137">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AC137">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD137">
         <v>0</v>
@@ -17579,10 +17579,10 @@
         <v>0</v>
       </c>
       <c r="AB138">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC138">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD138">
         <v>1.94</v>
@@ -17620,7 +17620,7 @@
         <v>71</v>
       </c>
       <c r="C139" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D139" t="s">
         <v>115</v>
@@ -17647,13 +17647,13 @@
         <v>405</v>
       </c>
       <c r="L139">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="M139">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N139">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="O139">
         <v>0</v>
@@ -17695,10 +17695,10 @@
         <v>0</v>
       </c>
       <c r="AB139">
-        <v>1.6</v>
+        <v>2.45</v>
       </c>
       <c r="AC139">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AD139">
         <v>0</v>
@@ -17763,13 +17763,13 @@
         <v>405</v>
       </c>
       <c r="L140">
-        <v>1.49</v>
+        <v>2.55</v>
       </c>
       <c r="M140">
-        <v>4.1</v>
+        <v>3.32</v>
       </c>
       <c r="N140">
-        <v>4.9</v>
+        <v>2.35</v>
       </c>
       <c r="O140">
         <v>0</v>
@@ -17852,7 +17852,7 @@
         <v>71</v>
       </c>
       <c r="C141" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D141" t="s">
         <v>115</v>
@@ -17879,13 +17879,13 @@
         <v>405</v>
       </c>
       <c r="L141">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
       <c r="M141">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="N141">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="O141">
         <v>0</v>
@@ -17927,10 +17927,10 @@
         <v>0</v>
       </c>
       <c r="AB141">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="AC141">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD141">
         <v>0</v>
@@ -18459,13 +18459,13 @@
         <v>405</v>
       </c>
       <c r="L146">
-        <v>2.75</v>
+        <v>1.87</v>
       </c>
       <c r="M146">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="N146">
-        <v>2.19</v>
+        <v>3.35</v>
       </c>
       <c r="O146">
         <v>0</v>
@@ -18575,13 +18575,13 @@
         <v>405</v>
       </c>
       <c r="L147">
-        <v>1.87</v>
+        <v>2.75</v>
       </c>
       <c r="M147">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="N147">
-        <v>3.35</v>
+        <v>2.19</v>
       </c>
       <c r="O147">
         <v>0</v>
@@ -18971,10 +18971,10 @@
         <v>0</v>
       </c>
       <c r="AB150">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC150">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD150">
         <v>2.25</v>
